--- a/Data/C04 Figures.xlsx
+++ b/Data/C04 Figures.xlsx
@@ -3266,10 +3266,21 @@
         <v>46023</v>
       </c>
       <c r="B262" t="n">
-        <v>18.0234273486055</v>
+        <v>17.9155004728868</v>
       </c>
       <c r="C262" t="n">
-        <v>5.10298086337017</v>
+        <v>4.93340527782551</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B263" t="n">
+        <v>17.9815691795725</v>
+      </c>
+      <c r="C263" t="n">
+        <v>5.23975192860384</v>
       </c>
     </row>
   </sheetData>
